--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/59.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/59.xlsx
@@ -426,13 +426,13 @@
         <v>-12.74813464563805</v>
       </c>
       <c r="E2">
-        <v>-26.02948953383651</v>
+        <v>-26.37723558135952</v>
       </c>
       <c r="F2">
-        <v>-5.35454550139104</v>
+        <v>-5.232191494160539</v>
       </c>
       <c r="G2">
-        <v>-16.11339296959867</v>
+        <v>-15.02017468998392</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.13667112005613</v>
       </c>
       <c r="E3">
-        <v>-24.7345316350771</v>
+        <v>-27.91141464804813</v>
       </c>
       <c r="F3">
-        <v>-4.631135561995842</v>
+        <v>-4.867429848746609</v>
       </c>
       <c r="G3">
-        <v>-15.80534670716948</v>
+        <v>-14.56983786973132</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.46265807984108</v>
       </c>
       <c r="E4">
-        <v>-27.32420742347351</v>
+        <v>-28.72768567335273</v>
       </c>
       <c r="F4">
-        <v>-5.112727660798405</v>
+        <v>-4.559605208396702</v>
       </c>
       <c r="G4">
-        <v>-16.89608042235701</v>
+        <v>-15.1099434428268</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.77088566733833</v>
       </c>
       <c r="E5">
-        <v>-27.18199975421064</v>
+        <v>-28.36480093722207</v>
       </c>
       <c r="F5">
-        <v>-4.461548873825116</v>
+        <v>-4.998585259631855</v>
       </c>
       <c r="G5">
-        <v>-16.02611043645578</v>
+        <v>-14.53608851323122</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.06994483364265</v>
       </c>
       <c r="E6">
-        <v>-26.82127962865565</v>
+        <v>-27.45705473696253</v>
       </c>
       <c r="F6">
-        <v>-5.246856910659701</v>
+        <v>-4.875851860130872</v>
       </c>
       <c r="G6">
-        <v>-14.87504037354227</v>
+        <v>-15.43522275006066</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.379253704978002</v>
       </c>
       <c r="E7">
-        <v>-26.95105663676746</v>
+        <v>-27.62774650773365</v>
       </c>
       <c r="F7">
-        <v>-4.822601918376711</v>
+        <v>-4.558785124667931</v>
       </c>
       <c r="G7">
-        <v>-15.19591499993613</v>
+        <v>-16.67094346241333</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.708907648123319</v>
       </c>
       <c r="E8">
-        <v>-26.79562129492819</v>
+        <v>-26.36249539846456</v>
       </c>
       <c r="F8">
-        <v>-4.539103115177414</v>
+        <v>-4.419276456892854</v>
       </c>
       <c r="G8">
-        <v>-15.8646187145046</v>
+        <v>-15.26425293623054</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.070428509655761</v>
       </c>
       <c r="E9">
-        <v>-28.52106046133075</v>
+        <v>-28.83111149121391</v>
       </c>
       <c r="F9">
-        <v>-4.452875867117806</v>
+        <v>-4.158774789530077</v>
       </c>
       <c r="G9">
-        <v>-15.75125901414887</v>
+        <v>-13.865550756434</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.468710003154555</v>
       </c>
       <c r="E10">
-        <v>-27.1796177768826</v>
+        <v>-27.78892395461465</v>
       </c>
       <c r="F10">
-        <v>-4.440561357307788</v>
+        <v>-4.443471411993823</v>
       </c>
       <c r="G10">
-        <v>-16.26449785492039</v>
+        <v>-15.67770862390288</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.906408419503369</v>
       </c>
       <c r="E11">
-        <v>-27.44283985705245</v>
+        <v>-28.55745127845639</v>
       </c>
       <c r="F11">
-        <v>-4.511523450868608</v>
+        <v>-4.419447100577831</v>
       </c>
       <c r="G11">
-        <v>-15.40459854854963</v>
+        <v>-14.82746617887017</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.383002704060682</v>
       </c>
       <c r="E12">
-        <v>-28.59025554416795</v>
+        <v>-29.57005429436354</v>
       </c>
       <c r="F12">
-        <v>-4.276681292174947</v>
+        <v>-3.812383019640631</v>
       </c>
       <c r="G12">
-        <v>-15.22333624863791</v>
+        <v>-15.66369508463515</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.893709717473063</v>
       </c>
       <c r="E13">
-        <v>-28.44027248503391</v>
+        <v>-30.38044283193218</v>
       </c>
       <c r="F13">
-        <v>-3.598551571751577</v>
+        <v>-3.329970008741894</v>
       </c>
       <c r="G13">
-        <v>-15.80029481467656</v>
+        <v>-14.99025728994553</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.440760249937571</v>
       </c>
       <c r="E14">
-        <v>-26.38490681632852</v>
+        <v>-29.02517471633862</v>
       </c>
       <c r="F14">
-        <v>-3.662536326678617</v>
+        <v>-3.43513704909911</v>
       </c>
       <c r="G14">
-        <v>-13.81719196246909</v>
+        <v>-14.93174174226614</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.022149838490633</v>
       </c>
       <c r="E15">
-        <v>-28.70600333980401</v>
+        <v>-30.08672827203169</v>
       </c>
       <c r="F15">
-        <v>-4.113130088901019</v>
+        <v>-4.054258017584058</v>
       </c>
       <c r="G15">
-        <v>-14.93104156188458</v>
+        <v>-14.42625950969313</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.63707166470125</v>
       </c>
       <c r="E16">
-        <v>-28.9139916225023</v>
+        <v>-30.05373833888581</v>
       </c>
       <c r="F16">
-        <v>-3.345009018939719</v>
+        <v>-3.007726805378858</v>
       </c>
       <c r="G16">
-        <v>-16.45839650715551</v>
+        <v>-14.57654006917558</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.285968089834394</v>
       </c>
       <c r="E17">
-        <v>-30.54594497149051</v>
+        <v>-32.38283441169585</v>
       </c>
       <c r="F17">
-        <v>-3.924444561891347</v>
+        <v>-2.892238307182759</v>
       </c>
       <c r="G17">
-        <v>-14.14738080873769</v>
+        <v>-15.229033697511</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.969749861387212</v>
       </c>
       <c r="E18">
-        <v>-28.69853588616536</v>
+        <v>-32.20286606192001</v>
       </c>
       <c r="F18">
-        <v>-4.076381225810625</v>
+        <v>-2.863377986869224</v>
       </c>
       <c r="G18">
-        <v>-13.91795172650235</v>
+        <v>-14.78157870715034</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.689198564836221</v>
       </c>
       <c r="E19">
-        <v>-29.38685487838324</v>
+        <v>-29.88921661395014</v>
       </c>
       <c r="F19">
-        <v>-2.920407769082359</v>
+        <v>-2.434629101426048</v>
       </c>
       <c r="G19">
-        <v>-14.40049518903375</v>
+        <v>-14.10570600621658</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.443853555489283</v>
       </c>
       <c r="E20">
-        <v>-30.65211504460034</v>
+        <v>-29.39923572632021</v>
       </c>
       <c r="F20">
-        <v>-3.281714294059211</v>
+        <v>-3.098570544974268</v>
       </c>
       <c r="G20">
-        <v>-14.21171132965681</v>
+        <v>-14.76124368117536</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.233054716901686</v>
       </c>
       <c r="E21">
-        <v>-30.43833257940923</v>
+        <v>-32.84733584032162</v>
       </c>
       <c r="F21">
-        <v>-2.980140514130829</v>
+        <v>-2.495550553697535</v>
       </c>
       <c r="G21">
-        <v>-14.42816141810544</v>
+        <v>-13.35123929890775</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.055330196815837</v>
       </c>
       <c r="E22">
-        <v>-30.6248762734442</v>
+        <v>-31.09251140608329</v>
       </c>
       <c r="F22">
-        <v>-2.717833834197351</v>
+        <v>-2.014414885333915</v>
       </c>
       <c r="G22">
-        <v>-13.92468206558369</v>
+        <v>-14.49049402479161</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.912139270294849</v>
       </c>
       <c r="E23">
-        <v>-29.57017203468774</v>
+        <v>-32.39556621636841</v>
       </c>
       <c r="F23">
-        <v>-2.953806714395832</v>
+        <v>-2.700167242597846</v>
       </c>
       <c r="G23">
-        <v>-13.30303444531043</v>
+        <v>-13.10308411582952</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.80332068619353</v>
       </c>
       <c r="E24">
-        <v>-30.77240263542908</v>
+        <v>-32.51346730139511</v>
       </c>
       <c r="F24">
-        <v>-2.639544002591367</v>
+        <v>-2.245294962739985</v>
       </c>
       <c r="G24">
-        <v>-14.04932907095556</v>
+        <v>-13.35208348802027</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.72835565531214</v>
       </c>
       <c r="E25">
-        <v>-29.56687077713615</v>
+        <v>-31.86519134059006</v>
       </c>
       <c r="F25">
-        <v>-2.869583287083596</v>
+        <v>-2.403747564649682</v>
       </c>
       <c r="G25">
-        <v>-13.71065364119704</v>
+        <v>-14.56831501878326</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.686213028333699</v>
       </c>
       <c r="E26">
-        <v>-30.58002626687224</v>
+        <v>-30.71829416374844</v>
       </c>
       <c r="F26">
-        <v>-2.856124801890312</v>
+        <v>-2.945300209536484</v>
       </c>
       <c r="G26">
-        <v>-13.85792491478429</v>
+        <v>-14.52824086503038</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.675604314385087</v>
       </c>
       <c r="E27">
-        <v>-30.14113788723385</v>
+        <v>-31.21655310186439</v>
       </c>
       <c r="F27">
-        <v>-3.228516539451427</v>
+        <v>-2.872263883999055</v>
       </c>
       <c r="G27">
-        <v>-13.62839320563723</v>
+        <v>-14.25596835769856</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.694616641606875</v>
       </c>
       <c r="E28">
-        <v>-30.40471092413929</v>
+        <v>-30.84918970494015</v>
       </c>
       <c r="F28">
-        <v>-3.30402471331881</v>
+        <v>-2.869721624439863</v>
       </c>
       <c r="G28">
-        <v>-13.48702960056481</v>
+        <v>-13.98017011936741</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.740351235924993</v>
       </c>
       <c r="E29">
-        <v>-29.7482089902993</v>
+        <v>-31.28121518221992</v>
       </c>
       <c r="F29">
-        <v>-2.786453304743054</v>
+        <v>-2.444278753301259</v>
       </c>
       <c r="G29">
-        <v>-14.27531518583006</v>
+        <v>-15.20688614785328</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.808857119762131</v>
       </c>
       <c r="E30">
-        <v>-29.21559251988715</v>
+        <v>-32.20064710965625</v>
       </c>
       <c r="F30">
-        <v>-2.733517314234554</v>
+        <v>-2.489730444325466</v>
       </c>
       <c r="G30">
-        <v>-14.00434041234963</v>
+        <v>-14.87555185282809</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.897116869243696</v>
       </c>
       <c r="E31">
-        <v>-28.61079670226674</v>
+        <v>-30.56947039396036</v>
       </c>
       <c r="F31">
-        <v>-2.748533958512504</v>
+        <v>-2.527944689351412</v>
       </c>
       <c r="G31">
-        <v>-13.66658200370549</v>
+        <v>-15.61455334665021</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.002711360705245</v>
       </c>
       <c r="E32">
-        <v>-27.59404560416856</v>
+        <v>-31.1473082058131</v>
       </c>
       <c r="F32">
-        <v>-3.143290787581802</v>
+        <v>-2.791784677347472</v>
       </c>
       <c r="G32">
-        <v>-14.91754115717543</v>
+        <v>-14.47668573934731</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.122990604647833</v>
       </c>
       <c r="E33">
-        <v>-29.42206829226688</v>
+        <v>-31.51302550243556</v>
       </c>
       <c r="F33">
-        <v>-2.889664569662261</v>
+        <v>-2.721962417332904</v>
       </c>
       <c r="G33">
-        <v>-14.14243485370202</v>
+        <v>-12.88536608843935</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.255013498343704</v>
       </c>
       <c r="E34">
-        <v>-28.28939731652035</v>
+        <v>-29.57427256790168</v>
       </c>
       <c r="F34">
-        <v>-3.375988303069614</v>
+        <v>-3.298712393164657</v>
       </c>
       <c r="G34">
-        <v>-14.08276723617497</v>
+        <v>-13.78300726923058</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.39559850624232</v>
       </c>
       <c r="E35">
-        <v>-26.1361667960352</v>
+        <v>-28.85966351983227</v>
       </c>
       <c r="F35">
-        <v>-2.975886847517453</v>
+        <v>-3.47020681146403</v>
       </c>
       <c r="G35">
-        <v>-15.23030660227085</v>
+        <v>-13.71697843844982</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.541015983507791</v>
       </c>
       <c r="E36">
-        <v>-27.69954093465125</v>
+        <v>-28.4978293896714</v>
       </c>
       <c r="F36">
-        <v>-2.973624576140408</v>
+        <v>-2.76267087660868</v>
       </c>
       <c r="G36">
-        <v>-14.35398367947976</v>
+        <v>-15.01737727900323</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.686983754674861</v>
       </c>
       <c r="E37">
-        <v>-26.58137013267729</v>
+        <v>-29.0841399763925</v>
       </c>
       <c r="F37">
-        <v>-2.833691784255099</v>
+        <v>-2.798489483105731</v>
       </c>
       <c r="G37">
-        <v>-14.09974371370035</v>
+        <v>-15.05143451623849</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.828983460630119</v>
       </c>
       <c r="E38">
-        <v>-28.35999622629994</v>
+        <v>-28.97451920608882</v>
       </c>
       <c r="F38">
-        <v>-3.20404656637273</v>
+        <v>-2.874517043334669</v>
       </c>
       <c r="G38">
-        <v>-13.61197621030798</v>
+        <v>-14.54079445371529</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.961309094717658</v>
       </c>
       <c r="E39">
-        <v>-27.16525798580428</v>
+        <v>-26.97171553519046</v>
       </c>
       <c r="F39">
-        <v>-3.368137865193284</v>
+        <v>-2.501231497345934</v>
       </c>
       <c r="G39">
-        <v>-14.36729538309317</v>
+        <v>-13.53016435366874</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.080143737184684</v>
       </c>
       <c r="E40">
-        <v>-26.95878221342455</v>
+        <v>-28.71780001459399</v>
       </c>
       <c r="F40">
-        <v>-3.228210043512391</v>
+        <v>-2.622618799817368</v>
       </c>
       <c r="G40">
-        <v>-14.17174476863396</v>
+        <v>-14.01866514289806</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.180940720950906</v>
       </c>
       <c r="E41">
-        <v>-25.55818407301421</v>
+        <v>-27.22184126853012</v>
       </c>
       <c r="F41">
-        <v>-2.934845384545752</v>
+        <v>-3.198894121127317</v>
       </c>
       <c r="G41">
-        <v>-12.98208036582362</v>
+        <v>-14.9458463215362</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.260076945552449</v>
       </c>
       <c r="E42">
-        <v>-27.35177677323221</v>
+        <v>-28.19917652886554</v>
       </c>
       <c r="F42">
-        <v>-2.784558000125449</v>
+        <v>-3.73445518458967</v>
       </c>
       <c r="G42">
-        <v>-13.16431927666942</v>
+        <v>-12.64139543492277</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.314399898067331</v>
       </c>
       <c r="E43">
-        <v>-26.04805174879395</v>
+        <v>-29.61863349928083</v>
       </c>
       <c r="F43">
-        <v>-3.094806443495948</v>
+        <v>-2.641218133112425</v>
       </c>
       <c r="G43">
-        <v>-14.18303703946841</v>
+        <v>-11.92031557937749</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.342408820422598</v>
       </c>
       <c r="E44">
-        <v>-26.46614764002613</v>
+        <v>-26.11988240350362</v>
       </c>
       <c r="F44">
-        <v>-3.385999951499849</v>
+        <v>-3.423365948305329</v>
       </c>
       <c r="G44">
-        <v>-12.68273752761718</v>
+        <v>-13.00658502390531</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.344290734558213</v>
       </c>
       <c r="E45">
-        <v>-23.94073542627256</v>
+        <v>-25.64154422254741</v>
       </c>
       <c r="F45">
-        <v>-3.336932436762424</v>
+        <v>-2.811884184008999</v>
       </c>
       <c r="G45">
-        <v>-12.88289642146706</v>
+        <v>-12.61564932226385</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.321554826574617</v>
       </c>
       <c r="E46">
-        <v>-25.54698062831923</v>
+        <v>-29.0782348462865</v>
       </c>
       <c r="F46">
-        <v>-3.045730645084494</v>
+        <v>-3.178201503405385</v>
       </c>
       <c r="G46">
-        <v>-13.86289073309319</v>
+        <v>-13.96185287089863</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.277402658569506</v>
       </c>
       <c r="E47">
-        <v>-23.19692451356469</v>
+        <v>-27.93524347827649</v>
       </c>
       <c r="F47">
-        <v>-3.300331023069727</v>
+        <v>-2.382640763226351</v>
       </c>
       <c r="G47">
-        <v>-12.23114270005966</v>
+        <v>-12.67316011937207</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.215130557006186</v>
       </c>
       <c r="E48">
-        <v>-24.75551205515464</v>
+        <v>-26.79519561837147</v>
       </c>
       <c r="F48">
-        <v>-3.205767085468344</v>
+        <v>-3.06549549131529</v>
       </c>
       <c r="G48">
-        <v>-11.16709694773697</v>
+        <v>-14.00088420280663</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.141321519769311</v>
       </c>
       <c r="E49">
-        <v>-23.90021011237792</v>
+        <v>-25.52509451344016</v>
       </c>
       <c r="F49">
-        <v>-3.711270837720117</v>
+        <v>-3.220842543831892</v>
       </c>
       <c r="G49">
-        <v>-12.63828352211585</v>
+        <v>-13.17542615695368</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.06316339810857</v>
       </c>
       <c r="E50">
-        <v>-24.63944273786404</v>
+        <v>-26.29796917232926</v>
       </c>
       <c r="F50">
-        <v>-3.782143467601434</v>
+        <v>-3.572830763894653</v>
       </c>
       <c r="G50">
-        <v>-12.49012336705131</v>
+        <v>-11.97183097851409</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.989598943313303</v>
       </c>
       <c r="E51">
-        <v>-22.92999814165657</v>
+        <v>-26.49362642030467</v>
       </c>
       <c r="F51">
-        <v>-3.862471911385708</v>
+        <v>-3.222497621902686</v>
       </c>
       <c r="G51">
-        <v>-11.64366984138829</v>
+        <v>-13.59870919905935</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.927948408721377</v>
       </c>
       <c r="E52">
-        <v>-24.56613580062787</v>
+        <v>-25.51446165647015</v>
       </c>
       <c r="F52">
-        <v>-3.672089059567701</v>
+        <v>-3.545691791044135</v>
       </c>
       <c r="G52">
-        <v>-12.63127840775475</v>
+        <v>-13.0315366056348</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.884262925283811</v>
       </c>
       <c r="E53">
-        <v>-24.33828110245793</v>
+        <v>-25.23636353918511</v>
       </c>
       <c r="F53">
-        <v>-4.242126774334569</v>
+        <v>-3.55167343205975</v>
       </c>
       <c r="G53">
-        <v>-13.40571101521092</v>
+        <v>-13.91795834759343</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.862961808381728</v>
       </c>
       <c r="E54">
-        <v>-23.68632575652164</v>
+        <v>-25.50979732824225</v>
       </c>
       <c r="F54">
-        <v>-3.955155454982736</v>
+        <v>-2.391108334817767</v>
       </c>
       <c r="G54">
-        <v>-12.35585426106955</v>
+        <v>-13.02812012263827</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.866686904482386</v>
       </c>
       <c r="E55">
-        <v>-23.92980369001805</v>
+        <v>-28.1137242243408</v>
       </c>
       <c r="F55">
-        <v>-3.789576408306754</v>
+        <v>-3.30708718760696</v>
       </c>
       <c r="G55">
-        <v>-12.78299408872847</v>
+        <v>-13.21744029039257</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.896285559368484</v>
       </c>
       <c r="E56">
-        <v>-23.18717018055217</v>
+        <v>-25.77590857482899</v>
       </c>
       <c r="F56">
-        <v>-3.925634097481768</v>
+        <v>-3.033015205451521</v>
       </c>
       <c r="G56">
-        <v>-12.88023805339902</v>
+        <v>-13.27630841117189</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.949690568679577</v>
       </c>
       <c r="E57">
-        <v>-23.34525920815994</v>
+        <v>-24.81896503295011</v>
       </c>
       <c r="F57">
-        <v>-4.167262241939161</v>
+        <v>-3.502837031827706</v>
       </c>
       <c r="G57">
-        <v>-13.75480142123599</v>
+        <v>-12.90544785768057</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.025037969706957</v>
       </c>
       <c r="E58">
-        <v>-23.68556950136236</v>
+        <v>-23.94403215535015</v>
       </c>
       <c r="F58">
-        <v>-3.903091735349385</v>
+        <v>-3.239861031032766</v>
       </c>
       <c r="G58">
-        <v>-13.62867460200807</v>
+        <v>-12.56164439288172</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.118691299616791</v>
       </c>
       <c r="E59">
-        <v>-23.62699369007315</v>
+        <v>-25.84624030464212</v>
       </c>
       <c r="F59">
-        <v>-4.313316668931159</v>
+        <v>-3.902277450192433</v>
       </c>
       <c r="G59">
-        <v>-11.65063853974846</v>
+        <v>-13.00066576848109</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.228169432298995</v>
       </c>
       <c r="E60">
-        <v>-23.36041148218961</v>
+        <v>-24.63247794484024</v>
       </c>
       <c r="F60">
-        <v>-4.194364766623956</v>
+        <v>-3.211932624047381</v>
       </c>
       <c r="G60">
-        <v>-11.76318384590152</v>
+        <v>-13.6785198309201</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.348747044980025</v>
       </c>
       <c r="E61">
-        <v>-24.59514520512101</v>
+        <v>-24.07404464411037</v>
       </c>
       <c r="F61">
-        <v>-4.603802751173069</v>
+        <v>-3.559404585030078</v>
       </c>
       <c r="G61">
-        <v>-13.07082616009487</v>
+        <v>-13.67113731436753</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.475261599802703</v>
       </c>
       <c r="E62">
-        <v>-24.57182809245552</v>
+        <v>-25.42063167503122</v>
       </c>
       <c r="F62">
-        <v>-4.173299383570764</v>
+        <v>-3.662307697275444</v>
       </c>
       <c r="G62">
-        <v>-12.96374656462714</v>
+        <v>-13.28834224420714</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.602643483750161</v>
       </c>
       <c r="E63">
-        <v>-24.5091223128713</v>
+        <v>-25.56171628274019</v>
       </c>
       <c r="F63">
-        <v>-4.410173527503491</v>
+        <v>-3.794287333726475</v>
       </c>
       <c r="G63">
-        <v>-12.70927155011444</v>
+        <v>-13.12051744863933</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.72630979091746</v>
       </c>
       <c r="E64">
-        <v>-24.76421125372337</v>
+        <v>-24.55409458824148</v>
       </c>
       <c r="F64">
-        <v>-4.227469641509435</v>
+        <v>-3.781614140831046</v>
       </c>
       <c r="G64">
-        <v>-11.78305374022823</v>
+        <v>-13.11245958079674</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.842676875451842</v>
       </c>
       <c r="E65">
-        <v>-25.25998405960912</v>
+        <v>-24.40543384351767</v>
       </c>
       <c r="F65">
-        <v>-4.303649621340488</v>
+        <v>-3.957691915970109</v>
       </c>
       <c r="G65">
-        <v>-13.04822506569826</v>
+        <v>-13.19949051247864</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.94822935099012</v>
       </c>
       <c r="E66">
-        <v>-24.47162654808779</v>
+        <v>-25.30174564690785</v>
       </c>
       <c r="F66">
-        <v>-4.140582184629794</v>
+        <v>-3.99914176407139</v>
       </c>
       <c r="G66">
-        <v>-12.93375964313242</v>
+        <v>-13.06753547782883</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.041732989651472</v>
       </c>
       <c r="E67">
-        <v>-24.1578395271483</v>
+        <v>-27.51075791021949</v>
       </c>
       <c r="F67">
-        <v>-4.642592711543962</v>
+        <v>-4.096175064900518</v>
       </c>
       <c r="G67">
-        <v>-13.36128680461944</v>
+        <v>-13.84531835737074</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.123172969873396</v>
       </c>
       <c r="E68">
-        <v>-24.3161821493005</v>
+        <v>-25.58778670760235</v>
       </c>
       <c r="F68">
-        <v>-3.972914823731355</v>
+        <v>-3.673520478439738</v>
       </c>
       <c r="G68">
-        <v>-11.84973805902577</v>
+        <v>-13.72180686911884</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.195192523574541</v>
       </c>
       <c r="E69">
-        <v>-25.46270119856248</v>
+        <v>-25.22604314692163</v>
       </c>
       <c r="F69">
-        <v>-4.247491281635098</v>
+        <v>-4.017481818369371</v>
       </c>
       <c r="G69">
-        <v>-12.64804301036562</v>
+        <v>-13.05671992555203</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.260258778892251</v>
       </c>
       <c r="E70">
-        <v>-24.71747287349021</v>
+        <v>-25.29023879445436</v>
       </c>
       <c r="F70">
-        <v>-4.601658107967221</v>
+        <v>-3.381801785502462</v>
       </c>
       <c r="G70">
-        <v>-12.68579647169547</v>
+        <v>-12.16187284519595</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.321135302049793</v>
       </c>
       <c r="E71">
-        <v>-24.85718988204886</v>
+        <v>-26.56273546213572</v>
       </c>
       <c r="F71">
-        <v>-4.651461212958334</v>
+        <v>-4.600165389907377</v>
       </c>
       <c r="G71">
-        <v>-10.94086750776533</v>
+        <v>-13.16593151234705</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.380650344048745</v>
       </c>
       <c r="E72">
-        <v>-23.67251843927226</v>
+        <v>-24.85711742646474</v>
       </c>
       <c r="F72">
-        <v>-4.661011460745209</v>
+        <v>-3.656644149342504</v>
       </c>
       <c r="G72">
-        <v>-12.59673286505246</v>
+        <v>-14.76352630232469</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.441323578918914</v>
       </c>
       <c r="E73">
-        <v>-25.86191335318267</v>
+        <v>-25.27859155930663</v>
       </c>
       <c r="F73">
-        <v>-4.466779185606392</v>
+        <v>-4.419566385483835</v>
       </c>
       <c r="G73">
-        <v>-14.05171431901661</v>
+        <v>-12.91208219094127</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.504799287506192</v>
       </c>
       <c r="E74">
-        <v>-25.70186802480358</v>
+        <v>-26.89866219249872</v>
       </c>
       <c r="F74">
-        <v>-4.732854108855205</v>
+        <v>-4.170748011970141</v>
       </c>
       <c r="G74">
-        <v>-12.70942383520925</v>
+        <v>-13.64849152760614</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.570854358938406</v>
       </c>
       <c r="E75">
-        <v>-25.75612367188948</v>
+        <v>-26.94593040419078</v>
       </c>
       <c r="F75">
-        <v>-4.435901790667041</v>
+        <v>-4.136892636217725</v>
       </c>
       <c r="G75">
-        <v>-12.48817345572868</v>
+        <v>-13.54668563118248</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.637639087476892</v>
       </c>
       <c r="E76">
-        <v>-25.23687525674798</v>
+        <v>-28.15134678639652</v>
       </c>
       <c r="F76">
-        <v>-4.637026082597149</v>
+        <v>-4.136723649267554</v>
       </c>
       <c r="G76">
-        <v>-12.95052093519775</v>
+        <v>-11.6916793727988</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.702910523862155</v>
       </c>
       <c r="E77">
-        <v>-25.17903758672201</v>
+        <v>-25.95793511604131</v>
       </c>
       <c r="F77">
-        <v>-4.901939634747237</v>
+        <v>-4.645033910280012</v>
       </c>
       <c r="G77">
-        <v>-12.01060077732449</v>
+        <v>-12.70319669904988</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.763940218243973</v>
       </c>
       <c r="E78">
-        <v>-26.5372175111025</v>
+        <v>-27.1991581422257</v>
       </c>
       <c r="F78">
-        <v>-5.165734062536142</v>
+        <v>-5.341367004379902</v>
       </c>
       <c r="G78">
-        <v>-12.47201468295149</v>
+        <v>-13.50921522149624</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.816535600215738</v>
       </c>
       <c r="E79">
-        <v>-25.16282564977455</v>
+        <v>-26.49444154562605</v>
       </c>
       <c r="F79">
-        <v>-4.983459270856736</v>
+        <v>-4.601055884865387</v>
       </c>
       <c r="G79">
-        <v>-13.70212071006957</v>
+        <v>-13.78095473099623</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.855631852803016</v>
       </c>
       <c r="E80">
-        <v>-25.66614289335707</v>
+        <v>-27.4918107749714</v>
       </c>
       <c r="F80">
-        <v>-5.601145507000036</v>
+        <v>-4.437488942610805</v>
       </c>
       <c r="G80">
-        <v>-13.14319468558333</v>
+        <v>-13.57579360283652</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.876471888809498</v>
       </c>
       <c r="E81">
-        <v>-27.72145422037437</v>
+        <v>-27.46425953910873</v>
       </c>
       <c r="F81">
-        <v>-4.6965459372231</v>
+        <v>-5.08694472538627</v>
       </c>
       <c r="G81">
-        <v>-12.88118155887772</v>
+        <v>-13.33044576237559</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.875110690236188</v>
       </c>
       <c r="E82">
-        <v>-28.42511115405623</v>
+        <v>-29.46120336464117</v>
       </c>
       <c r="F82">
-        <v>-4.532683267805719</v>
+        <v>-4.896459156010316</v>
       </c>
       <c r="G82">
-        <v>-12.14315171017137</v>
+        <v>-13.20678695484719</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.848630348853903</v>
       </c>
       <c r="E83">
-        <v>-27.44808382995333</v>
+        <v>-29.23769600151859</v>
       </c>
       <c r="F83">
-        <v>-5.049813156555782</v>
+        <v>-4.802458508242836</v>
       </c>
       <c r="G83">
-        <v>-13.0473014234928</v>
+        <v>-13.49523478768389</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.795076565157522</v>
       </c>
       <c r="E84">
-        <v>-28.40570664293336</v>
+        <v>-28.15494692323262</v>
       </c>
       <c r="F84">
-        <v>-5.25284849208415</v>
+        <v>-5.58766879772389</v>
       </c>
       <c r="G84">
-        <v>-13.64036413830723</v>
+        <v>-12.84560643651271</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.712885600572271</v>
       </c>
       <c r="E85">
-        <v>-29.12687971407689</v>
+        <v>-28.87134698277207</v>
       </c>
       <c r="F85">
-        <v>-5.303991895532991</v>
+        <v>-4.711018344117409</v>
       </c>
       <c r="G85">
-        <v>-14.08318436491292</v>
+        <v>-13.74447086388069</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.603285351573772</v>
       </c>
       <c r="E86">
-        <v>-28.09988520777336</v>
+        <v>-31.86475434284832</v>
       </c>
       <c r="F86">
-        <v>-5.788012767560562</v>
+        <v>-5.658489240458831</v>
       </c>
       <c r="G86">
-        <v>-14.38093152016943</v>
+        <v>-12.82467716761344</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.469646913852512</v>
       </c>
       <c r="E87">
-        <v>-29.96484212987824</v>
+        <v>-31.25137480274637</v>
       </c>
       <c r="F87">
-        <v>-5.022467920221968</v>
+        <v>-5.17383798083773</v>
       </c>
       <c r="G87">
-        <v>-13.68298079103427</v>
+        <v>-14.21669866651172</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.317253638064548</v>
       </c>
       <c r="E88">
-        <v>-30.32037941693144</v>
+        <v>-32.84231829112112</v>
       </c>
       <c r="F88">
-        <v>-5.185339033858198</v>
+        <v>-5.26466101124807</v>
       </c>
       <c r="G88">
-        <v>-13.37677353665215</v>
+        <v>-13.40566135702783</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.151767878937647</v>
       </c>
       <c r="E89">
-        <v>-32.63487116106675</v>
+        <v>-31.80772726966973</v>
       </c>
       <c r="F89">
-        <v>-5.859799086687167</v>
+        <v>-5.99172902109403</v>
       </c>
       <c r="G89">
-        <v>-14.23210097963318</v>
+        <v>-13.34893515921242</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.979628699366799</v>
       </c>
       <c r="E90">
-        <v>-32.58349335921272</v>
+        <v>-33.33971229070161</v>
       </c>
       <c r="F90">
-        <v>-5.630714909810367</v>
+        <v>-5.61801023895363</v>
       </c>
       <c r="G90">
-        <v>-14.32230175866894</v>
+        <v>-13.75684402783372</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.807573924594544</v>
       </c>
       <c r="E91">
-        <v>-35.32483000636302</v>
+        <v>-33.43100632669624</v>
       </c>
       <c r="F91">
-        <v>-5.496944343034483</v>
+        <v>-5.110814132097938</v>
       </c>
       <c r="G91">
-        <v>-13.81003456301319</v>
+        <v>-14.88514746907367</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.642380006852191</v>
       </c>
       <c r="E92">
-        <v>-34.02106422565869</v>
+        <v>-35.61580710372587</v>
       </c>
       <c r="F92">
-        <v>-6.304923138948884</v>
+        <v>-5.369551376892752</v>
       </c>
       <c r="G92">
-        <v>-13.69364571348903</v>
+        <v>-14.7382585634962</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.490467698163222</v>
       </c>
       <c r="E93">
-        <v>-35.76736380757758</v>
+        <v>-35.87412258230841</v>
       </c>
       <c r="F93">
-        <v>-5.957809032684196</v>
+        <v>-5.871888280563623</v>
       </c>
       <c r="G93">
-        <v>-13.81937692252501</v>
+        <v>-14.17858435571809</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.356134966570944</v>
       </c>
       <c r="E94">
-        <v>-38.23357528062887</v>
+        <v>-36.33233396053753</v>
       </c>
       <c r="F94">
-        <v>-5.840967810519325</v>
+        <v>-5.393622905250703</v>
       </c>
       <c r="G94">
-        <v>-14.79731207482572</v>
+        <v>-14.34930256808723</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.244606633182735</v>
       </c>
       <c r="E95">
-        <v>-38.88582724161265</v>
+        <v>-39.18366724133413</v>
       </c>
       <c r="F95">
-        <v>-6.601914804588681</v>
+        <v>-6.227703558027317</v>
       </c>
       <c r="G95">
-        <v>-14.54934228229769</v>
+        <v>-14.38537427228313</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.16069675810062</v>
       </c>
       <c r="E96">
-        <v>-38.40336814930946</v>
+        <v>-42.20544549106845</v>
       </c>
       <c r="F96">
-        <v>-5.921149633273304</v>
+        <v>-6.704971993170967</v>
       </c>
       <c r="G96">
-        <v>-15.1075830238573</v>
+        <v>-16.34433993696377</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.10744175877819</v>
       </c>
       <c r="E97">
-        <v>-39.8615865929934</v>
+        <v>-43.72406698530369</v>
       </c>
       <c r="F97">
-        <v>-5.842414140004614</v>
+        <v>-6.029154660352511</v>
       </c>
       <c r="G97">
-        <v>-14.62458105076871</v>
+        <v>-14.41589750215521</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.089697890810525</v>
       </c>
       <c r="E98">
-        <v>-42.8431542577766</v>
+        <v>-44.54195014735503</v>
       </c>
       <c r="F98">
-        <v>-6.028530899698204</v>
+        <v>-6.236693415266198</v>
       </c>
       <c r="G98">
-        <v>-14.36619462670136</v>
+        <v>-14.61238831154757</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.104637892754192</v>
       </c>
       <c r="E99">
-        <v>-45.30279491504275</v>
+        <v>-43.68580137993888</v>
       </c>
       <c r="F99">
-        <v>-6.133211688389977</v>
+        <v>-6.681491504954914</v>
       </c>
       <c r="G99">
-        <v>-14.48672662396792</v>
+        <v>-15.28652794189152</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.158729213181228</v>
       </c>
       <c r="E100">
-        <v>-47.00057189796946</v>
+        <v>-48.46083721190487</v>
       </c>
       <c r="F100">
-        <v>-6.088006022484403</v>
+        <v>-7.233725119133413</v>
       </c>
       <c r="G100">
-        <v>-15.77178770703789</v>
+        <v>-14.97040394834652</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.240938191347657</v>
       </c>
       <c r="E101">
-        <v>-47.54645226875007</v>
+        <v>-49.1964187552223</v>
       </c>
       <c r="F101">
-        <v>-6.569074178904694</v>
+        <v>-7.801966519187311</v>
       </c>
       <c r="G101">
-        <v>-15.27849821368602</v>
+        <v>-16.06449621198363</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.36615286913229</v>
       </c>
       <c r="E102">
-        <v>-49.17401413006935</v>
+        <v>-50.69602405498084</v>
       </c>
       <c r="F102">
-        <v>-6.595760448969582</v>
+        <v>-7.249989284719978</v>
       </c>
       <c r="G102">
-        <v>-16.33569279201519</v>
+        <v>-15.85279675638386</v>
       </c>
     </row>
   </sheetData>
